--- a/data/pest_disease_control.xlsx
+++ b/data/pest_disease_control.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L442"/>
+  <dimension ref="A1:L449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19740,35 +19740,315 @@
           <t>R579</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>7.78</t>
-        </is>
-      </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D442" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E442" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="F442" t="n">
+        <v>0</v>
+      </c>
+      <c r="G442" t="n">
+        <v>0</v>
       </c>
       <c r="H442" t="inlineStr"/>
       <c r="I442" t="inlineStr"/>
       <c r="J442" t="inlineStr"/>
-      <c r="K442" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="K442" t="n">
+        <v>9</v>
       </c>
       <c r="L442" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>DG14000</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E443" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="F443" t="n">
+        <v>0</v>
+      </c>
+      <c r="G443" t="n">
+        <v>0</v>
+      </c>
+      <c r="H443" t="inlineStr"/>
+      <c r="I443" t="inlineStr"/>
+      <c r="J443" t="inlineStr"/>
+      <c r="K443" t="n">
+        <v>16</v>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>DG11000</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>MN1</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E444" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="F444" t="n">
+        <v>0</v>
+      </c>
+      <c r="G444" t="n">
+        <v>0</v>
+      </c>
+      <c r="H444" t="inlineStr"/>
+      <c r="I444" t="inlineStr"/>
+      <c r="J444" t="inlineStr"/>
+      <c r="K444" t="n">
+        <v>18</v>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>DG36000</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E445" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="F445" t="n">
+        <v>0</v>
+      </c>
+      <c r="G445" t="n">
+        <v>0</v>
+      </c>
+      <c r="H445" t="inlineStr"/>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
+      <c r="K445" t="n">
+        <v>8</v>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>DG04000</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E446" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="F446" t="n">
+        <v>0</v>
+      </c>
+      <c r="G446" t="n">
+        <v>0</v>
+      </c>
+      <c r="H446" t="inlineStr"/>
+      <c r="I446" t="inlineStr"/>
+      <c r="J446" t="inlineStr"/>
+      <c r="K446" t="n">
+        <v>10</v>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>DG02000</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E447" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="F447" t="n">
+        <v>0</v>
+      </c>
+      <c r="G447" t="n">
+        <v>0</v>
+      </c>
+      <c r="H447" t="inlineStr"/>
+      <c r="I447" t="inlineStr"/>
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="n">
+        <v>5</v>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>DG20000</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E448" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="F448" t="n">
+        <v>0</v>
+      </c>
+      <c r="G448" t="n">
+        <v>0</v>
+      </c>
+      <c r="H448" t="inlineStr"/>
+      <c r="I448" t="inlineStr"/>
+      <c r="J448" t="inlineStr"/>
+      <c r="K448" t="n">
+        <v>9</v>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>DG37000</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>26.43</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr"/>
+      <c r="I449" t="inlineStr"/>
+      <c r="J449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
         <is>
           <t>2026/27</t>
         </is>

--- a/data/pest_disease_control.xlsx
+++ b/data/pest_disease_control.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L449"/>
+  <dimension ref="A1:L458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20020,35 +20020,395 @@
           <t>R579</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="E449" t="inlineStr">
-        <is>
-          <t>26.43</t>
-        </is>
-      </c>
-      <c r="F449" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G449" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D449" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E449" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="F449" t="n">
+        <v>0</v>
+      </c>
+      <c r="G449" t="n">
+        <v>0</v>
       </c>
       <c r="H449" t="inlineStr"/>
       <c r="I449" t="inlineStr"/>
       <c r="J449" t="inlineStr"/>
-      <c r="K449" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="K449" t="n">
+        <v>6</v>
       </c>
       <c r="L449" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>DG31000</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E450" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="F450" t="n">
+        <v>0</v>
+      </c>
+      <c r="G450" t="n">
+        <v>0</v>
+      </c>
+      <c r="H450" t="inlineStr"/>
+      <c r="I450" t="inlineStr"/>
+      <c r="J450" t="inlineStr"/>
+      <c r="K450" t="n">
+        <v>16</v>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>DG32000</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E451" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F451" t="n">
+        <v>0</v>
+      </c>
+      <c r="G451" t="n">
+        <v>0</v>
+      </c>
+      <c r="H451" t="inlineStr"/>
+      <c r="I451" t="inlineStr"/>
+      <c r="J451" t="inlineStr"/>
+      <c r="K451" t="n">
+        <v>16</v>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>DG04000</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E452" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="F452" t="n">
+        <v>0</v>
+      </c>
+      <c r="G452" t="n">
+        <v>0</v>
+      </c>
+      <c r="H452" t="inlineStr"/>
+      <c r="I452" t="inlineStr"/>
+      <c r="J452" t="inlineStr"/>
+      <c r="K452" t="n">
+        <v>5</v>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>DG02000</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E453" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="F453" t="n">
+        <v>0</v>
+      </c>
+      <c r="G453" t="n">
+        <v>0</v>
+      </c>
+      <c r="H453" t="inlineStr"/>
+      <c r="I453" t="inlineStr"/>
+      <c r="J453" t="inlineStr"/>
+      <c r="K453" t="n">
+        <v>5</v>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>DG20000</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E454" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="F454" t="n">
+        <v>0</v>
+      </c>
+      <c r="G454" t="n">
+        <v>0</v>
+      </c>
+      <c r="H454" t="inlineStr"/>
+      <c r="I454" t="inlineStr"/>
+      <c r="J454" t="inlineStr"/>
+      <c r="K454" t="n">
+        <v>6</v>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>DG22000</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E455" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="F455" t="n">
+        <v>0</v>
+      </c>
+      <c r="G455" t="n">
+        <v>0</v>
+      </c>
+      <c r="H455" t="inlineStr"/>
+      <c r="I455" t="inlineStr"/>
+      <c r="J455" t="inlineStr"/>
+      <c r="K455" t="n">
+        <v>16</v>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>DG25000</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E456" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="F456" t="n">
+        <v>0</v>
+      </c>
+      <c r="G456" t="n">
+        <v>0</v>
+      </c>
+      <c r="H456" t="inlineStr"/>
+      <c r="I456" t="inlineStr"/>
+      <c r="J456" t="inlineStr"/>
+      <c r="K456" t="n">
+        <v>9</v>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>DG26000</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E457" t="n">
+        <v>20</v>
+      </c>
+      <c r="F457" t="n">
+        <v>0</v>
+      </c>
+      <c r="G457" t="n">
+        <v>0</v>
+      </c>
+      <c r="H457" t="inlineStr"/>
+      <c r="I457" t="inlineStr"/>
+      <c r="J457" t="inlineStr"/>
+      <c r="K457" t="n">
+        <v>13</v>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>DG35000</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr"/>
+      <c r="I458" t="inlineStr"/>
+      <c r="J458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
         <is>
           <t>2026/27</t>
         </is>

--- a/data/pest_disease_control.xlsx
+++ b/data/pest_disease_control.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7320"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
